--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/INDIANA_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/INDIANA_2024.xlsx
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C178">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C302">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C676">
